--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,210 +159,252 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>83197</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9845.8</t>
+          <t>153197</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>18936.71</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1183.8</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10274.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,210 +201,252 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>153197</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18936.71</t>
+          <t>179195</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>22013.39</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>10274.71</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13351.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,210 +243,252 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>179195</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>22013.39</t>
+          <t>324195</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>39483.27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>13351.39</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>30821.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -412,83 +412,110 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>324195</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>39483.27</t>
+          <t>324195</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>39483.27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>26131</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>30821.27</t>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13352.27</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,237 +285,279 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>324195</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>39483.27</t>
+          <t>634195</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>77520.08</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>26131</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>13352.27</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>51389.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -454,12 +454,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -481,83 +481,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>634195</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>77520.08</t>
+          <t>634195</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>77520.08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>46131</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>51389.08</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>31389.08</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,166 +327,181 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -496,7 +511,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -508,83 +523,110 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>634195</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>77520.08</t>
+          <t>642394</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>46131</t>
+          <t>78490.38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>46131</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>31389.08</t>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>32359.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,166 +369,181 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -538,7 +553,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -550,83 +565,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>642394</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>78490.38</t>
+          <t>792394</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>46131</t>
+          <t>96672.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>46131</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>32359.38</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>50541.2</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,166 +411,181 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -580,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -592,83 +607,110 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>792394</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>96672.2</t>
+          <t>902394</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>46131</t>
+          <t>110005.53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>46131</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>50541.2</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>63874.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,83 +634,110 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>902394</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>110005.53</t>
+          <t>902394</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>46131</t>
+          <t>110005.53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>64131</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>63874.53</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>45874.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -580,12 +580,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -607,12 +607,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -634,12 +634,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,83 +661,110 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>902394</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>110005.53</t>
+          <t>902394</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>64131</t>
+          <t>110005.53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>45874.53</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>31390.53</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,166 +453,181 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -634,12 +649,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -649,7 +664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -661,12 +676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -676,7 +691,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -688,83 +703,110 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>902394</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>110005.53</t>
+          <t>967188</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>117673.46</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>31390.53</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>39058.46</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,166 +495,181 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -676,12 +691,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -691,7 +706,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -703,12 +718,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -718,7 +733,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -730,83 +745,110 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>967188</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>117673.46</t>
+          <t>976387</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>118755.7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>39058.46</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>40140.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,166 +537,181 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -718,12 +733,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -733,7 +748,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -745,12 +760,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -760,7 +775,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -772,83 +787,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>976387</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>118755.7</t>
+          <t>989386</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>120284.99</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>40140.7</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>41669.99</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,166 +579,181 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -760,12 +775,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -775,7 +790,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -787,12 +802,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -802,7 +817,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -814,83 +829,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>989386</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>120284.99</t>
+          <t>1030386</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>125679.73</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>41669.99</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>47064.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,166 +621,181 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -802,12 +817,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -817,7 +832,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -829,12 +844,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -844,7 +859,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -856,83 +871,110 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1030386</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>125679.73</t>
+          <t>1130386</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>137727.92</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>47064.73</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>59112.92</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,166 +663,181 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -844,12 +859,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -859,7 +874,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -871,12 +886,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -886,7 +901,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -898,83 +913,110 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1130386</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>137727.92</t>
+          <t>1141385</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>139021.92</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>59112.92</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>60406.92</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,166 +705,181 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -886,12 +901,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -901,7 +916,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -913,12 +928,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -928,7 +943,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -940,83 +955,110 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1141385</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>139021.92</t>
+          <t>1241385</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>151143.13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>60406.92</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>72528.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,166 +747,181 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -928,12 +943,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -943,7 +958,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -955,12 +970,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -970,7 +985,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -982,83 +997,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1241385</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>151143.13</t>
+          <t>1341965.35</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>163046.13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>72528.13</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>84431.13</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,166 +789,181 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -970,12 +985,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -985,7 +1000,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -997,12 +1012,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1012,7 +1027,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1024,83 +1039,110 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1341965.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>163046.13</t>
+          <t>1389562.35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>168645.78</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>84431.13</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>90030.78</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,166 +831,181 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1012,12 +1027,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1027,7 +1042,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1039,12 +1054,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1054,7 +1069,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1066,83 +1081,110 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1389562.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>168645.78</t>
+          <t>1420159.35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>172245.43</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>90030.78</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>93630.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,166 +873,181 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1054,12 +1069,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1069,7 +1084,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1081,12 +1096,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1096,7 +1111,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1108,83 +1123,110 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1420159.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>172245.43</t>
+          <t>1427358.35</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>173082.52</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>93630.43</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>94467.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/18 16:38:21</t>
+          <t>10/23 12:46:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>837.09</t>
+          <t>3041.18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,166 +915,181 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1096,12 +1111,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1111,7 +1126,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1123,12 +1138,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1138,7 +1153,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1150,83 +1165,110 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1427358.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>173082.52</t>
+          <t>1453056.35</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>176123.7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>94467.52</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>97508.7</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/23 12:46:58</t>
+          <t>10/25 10:55:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3041.18</t>
+          <t>1823.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/18 16:38:21</t>
+          <t>10/23 12:46:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>837.09</t>
+          <t>3041.18</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,166 +957,181 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1138,12 +1153,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1153,7 +1168,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1165,12 +1180,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1180,7 +1195,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1192,83 +1207,110 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1453056.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>176123.7</t>
+          <t>1468555.35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>177947.11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>97508.7</t>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>99332.11</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/25 10:55:17</t>
+          <t>10/27 11:20:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1823.41</t>
+          <t>5223.06</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/23 12:46:58</t>
+          <t>10/25 10:55:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3041.18</t>
+          <t>1823.41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/18 16:38:21</t>
+          <t>10/23 12:46:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>837.09</t>
+          <t>3041.18</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,166 +999,181 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1180,12 +1195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1195,7 +1210,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1207,12 +1222,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1222,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1234,83 +1249,110 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1468555.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>177947.11</t>
+          <t>1512951.35</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>183170.17</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>99332.11</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>104555.17</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 11:20:39</t>
+          <t>10/29 10:37:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44396</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5223.06</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/25 10:55:17</t>
+          <t>10/27 11:20:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1823.41</t>
+          <t>5223.06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/23 12:46:58</t>
+          <t>10/25 10:55:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3041.18</t>
+          <t>1823.41</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/18 16:38:21</t>
+          <t>10/23 12:46:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>837.09</t>
+          <t>3041.18</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,166 +1041,181 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1222,12 +1237,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1252,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1249,12 +1264,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1264,7 +1279,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1276,83 +1291,110 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1512951.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>183170.17</t>
+          <t>1612951.35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>195365.29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>104555.17</t>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>116750.29</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/29 10:37:47</t>
+          <t>10/30 12:37:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_luxi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/27 11:20:39</t>
+          <t>10/29 10:37:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>44396</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5223.06</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/25 10:55:17</t>
+          <t>10/27 11:20:39</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1823.41</t>
+          <t>5223.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/23 12:46:58</t>
+          <t>10/25 10:55:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3041.18</t>
+          <t>1823.41</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/18 16:38:21</t>
+          <t>10/23 12:46:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>837.09</t>
+          <t>3041.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1083,166 +1083,181 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1264,12 +1279,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1279,7 +1294,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1291,12 +1306,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1321,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1318,83 +1333,110 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1612951.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>195365.29</t>
+          <t>1712951.35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>207560.42</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>116750.29</t>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>128945.42</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
+++ b/bills/JXZFSP01/-5565590984/18ba1de91cd6c66a34c318991e16670b1d58e4103e3c5e3e6d3fda1849aaeb12/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/30 12:37:08</t>
+          <t>10/30 20:12:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>13414.63</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>lh_luxi</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/29 10:37:47</t>
+          <t>10/30 12:37:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_luxi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/27 11:20:39</t>
+          <t>10/29 10:37:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44396</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5223.06</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10/25 10:55:17</t>
+          <t>10/27 11:20:39</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15499</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1823.41</t>
+          <t>5223.06</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10/23 12:46:58</t>
+          <t>10/25 10:55:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3041.18</t>
+          <t>1823.41</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10/18 16:38:21</t>
+          <t>10/23 12:46:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>837.09</t>
+          <t>3041.18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10/18 16:38:07</t>
+          <t>10/18 16:38:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30597</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3599.65</t>
+          <t>837.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10/17 10:37:05</t>
+          <t>10/18 16:38:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5599.65</t>
+          <t>3599.65</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/13 11:17:03</t>
+          <t>10/17 10:37:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>100580.35</t>
+          <t>47597</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11903</t>
+          <t>5599.65</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10/12 11:05:26</t>
+          <t>10/13 11:17:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>100580.35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10/10 10:45:35</t>
+          <t>10/12 11:05:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10/09 11:15:58</t>
+          <t>10/10 10:45:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10/08 11:40:17</t>
+          <t>10/09 11:15:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5394.74</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10/08 11:40:04</t>
+          <t>10/08 11:40:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1529.29</t>
+          <t>5394.74</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10/06 11:08:11</t>
+          <t>10/08 11:40:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1082.24</t>
+          <t>1529.29</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>lh_hhhhh</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/26 11:36:07</t>
+          <t>10/06 11:08:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>64794</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7667.93</t>
+          <t>1082.24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_hhhhh</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09/25 13:17:22</t>
+          <t>09/26 11:36:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>64794</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>13333.33</t>
+          <t>7667.93</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09/25 12:28:53</t>
+          <t>09/25 13:17:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18181.82</t>
+          <t>13333.33</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>09/25 11:26:04</t>
+          <t>09/25 12:28:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>970.3</t>
+          <t>18181.82</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09/24 18:06:31</t>
+          <t>09/25 11:26:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>310000</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38036.81</t>
+          <t>970.3</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>09/23 15:26:15</t>
+          <t>09/24 18:06:31</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>310000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17469.88</t>
+          <t>38036.81</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>09/20 09:36:57</t>
+          <t>09/23 15:26:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>145000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3076.69</t>
+          <t>17469.88</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>lh_zzzz</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>09/19 11:33:33</t>
+          <t>09/20 09:36:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9090.91</t>
+          <t>3076.69</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>lh_xxxx</t>
+          <t>lh_zzzz</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>09/17 11:42:19</t>
+          <t>09/19 11:33:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1183.31</t>
+          <t>9090.91</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/25 11:53:23</t>
+          <t>09/17 11:42:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6248.52</t>
+          <t>1183.31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>lh_xxxx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1125,166 +1125,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>07/25 11:53:23</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>52800</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6248.52</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>07/25 11:51:08</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>20398</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>8.45</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2413.96</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09/25 14:51:25</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09/25 13:18:04</t>
+          <t>09/25 14:51:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,12 +1321,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09/24 18:06:51</t>
+          <t>09/25 13:18:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1321,7 +1336,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1333,12 +1348,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09/23 17:03:42</t>
+          <t>09/24 18:06:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1348,7 +1363,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1360,83 +1375,110 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>09/23 17:03:42</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17469</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>07/25 12:36:13</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1712951.35</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>207560.42</t>
+          <t>1822951.35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>78615</t>
+          <t>220975.05</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>78615</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>128945.42</t>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>142360.05</t>
         </is>
       </c>
     </row>
